--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx
@@ -1284,33 +1284,33 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>INTERNET INTELIGENTE</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1348,14 +1348,14 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>1</v>
@@ -1380,14 +1380,14 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>GIIRA</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
@@ -1396,7 +1396,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>INTECSE</t>
+          <t>GITUD</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
@@ -1412,7 +1412,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GITUD</t>
+          <t>INTECSE</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
@@ -1476,7 +1476,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>GICOECOL</t>
+          <t>ARMOS</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -1492,7 +1492,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>ARMOS</t>
+          <t>GICOECOL</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -1524,14 +1524,14 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>LASER LAMIC</t>
+          <t>GITEM++</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>0</v>
@@ -1540,14 +1540,14 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>XUE</t>
+          <t>CEPMS</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1556,14 +1556,14 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>COMPLEX UD</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>LAMIC</t>
+          <t>PROPROBOS</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -1588,7 +1588,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PROPROBOS</t>
+          <t>LASER LAMIC</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
@@ -1604,7 +1604,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>CEPMS</t>
+          <t>Bionanotecnología</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -1620,7 +1620,7 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Bionanotecnología</t>
+          <t>COMPLEX UD</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
@@ -1636,14 +1636,14 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>DIMSI</t>
+          <t>LAMIC</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>GITEM++</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">

--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx
@@ -10,12 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativo por grupo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes sustentación" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes y calidad" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes por sustentar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesis con documento" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Consolidado'!$A$3:$M$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pendientes sustentación'!$A$3:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pendientes por sustentar'!$A$3:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tesis con documento'!$A$4:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -558,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -659,7 +660,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Pendientes / sin verificación</t>
+          <t>Pendientes por sustentar</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -679,7 +680,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -707,7 +708,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>No sustentados</t>
+          <t>Pendientes por sustentar</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -737,7 +738,7 @@
         <v>7</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -781,7 +782,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>3</v>
@@ -807,7 +808,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>No sustentados</t>
+          <t>Pendientes por sustentar</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -998,17 +999,17 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>LASER</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>LASER</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
@@ -1068,7 +1069,7 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>LASER LAMIC</t>
+          <t>GICOECOL</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
@@ -1078,7 +1079,7 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>GICOECOL</t>
+          <t>LAMIC</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
@@ -1088,7 +1089,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>LAMIC</t>
+          <t>IAFT</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
@@ -1098,7 +1099,7 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>IAFT</t>
+          <t>PROPROBOS</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
@@ -1108,20 +1109,10 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>PROPROBOS</t>
+          <t>CEPMS</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>CEPMS</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1158,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1226,27 +1217,27 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>INTERNET INTELIGENTE</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>INTERNET INTELIGENTE</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1278,46 +1269,46 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>GRECO</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>GRECO</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>GIIRA</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>GITUD</t>
+          <t>INTECSE</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -1330,27 +1321,27 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>INTECSE</t>
+          <t>LASER</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>LASER</t>
+          <t>GITUD</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1395,7 +1386,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>GICOECOL</t>
+          <t>ARMOS</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
@@ -1408,7 +1399,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ARMOS</t>
+          <t>GICOECOL</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -1434,20 +1425,20 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>DIMSI</t>
+          <t>Bionanotecnología</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>LASER LAMIC</t>
+          <t>COMPLEX UD</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -1460,46 +1451,46 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>PROPROBOS</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>CEPMS</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>XUE</t>
+          <t>CEPMS</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>COMPLEX UD</t>
+          <t>PROPROBOS</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
@@ -1519,19 +1510,6 @@
         <v>1</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Bionanotecnología</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4523,7 +4501,7 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>LASER LAMIC</t>
+          <t>LASER</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -7032,497 +7010,354 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fuentes, alcance y control de calidad (tomado del consolidado original)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Registros incorporados</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Uso en el consolidado</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Siete archivos de grupos de investigación</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Base inicial</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Aportaron 62 registros; 17 contenían enlace RIUD.</t>
+          <t>Trabajos de grado con documento completo — Investigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Documentos disponibles en la carpeta «Anexos / Tesis».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Grupo de investigación</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Título</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Estudiante(s)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Director(es)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Estado de sustentación</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Documento (anexo)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos V2.xlsx</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Se filtraron sustentaciones, grados y actas de pasantía de 2022 a 2026.</t>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Modelo de evaluación crediticio basado en principios de un ecosistema digital bancario mediante estrategias de Business Intelligence y mecanismos de reputación en el sector de industria de turismo de las PYMES colombianas</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>William Stiven Garces Rodriguez</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Paulo Alonso Gaona García</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Tesis - Modelo de evaluación crediticio basado en principios de un ecosistema digital bancario med.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos V2.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Registros cruzados</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Coincidencias por estudiante o título con la base inicial.</t>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Modelo de learning analytics basado en métricas emocionales para aplicaciones móviles de aprendizaje en segunda lengua</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Andres Ovidio Restrepo Rodriguez</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Paulo Alonso Gaona García</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Tesis - Modelo de learning analytics basado en métricas emocionales para aplicaciones móviles de a.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos V2.xlsx</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Actualización de grupo</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Permitió identificar el grupo de ocho registros previamente no especificados.</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>GIIRA</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Mejoramiento de la descripción de recursos educativos abiertos, a partir de técnicas basadas en inteligencia artificial, machine learning y minería de datos</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Juan Guillermo Cotta Garcia</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>John Francined Herrera Cubides</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Tesis - Mejoramiento de la descripción de recursos educativos abiertos, a partir de técnicas basad.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Trabajos con sustentación registrada en 2025 o 2026.</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>INTECSE</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>METAMODELO SOFTWARE DE SIMULACION REMOTA INTERACTIVA EN AMBIENTE WEB</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>PIÑEROS RAMIREZ JEISSON RODRIGO</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Julio Baron Velandia</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Tesis - METAMODELO SOFTWARE DE SIMULACION REMOTA INTERACTIVA EN AMBIENTE WEB.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Registros cruzados</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Dos coincidencias integradas sin duplicación.</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>INTECSE</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>MODELO DE INFERENCIA ONTOLOGICA PARA CARACTERIZACION DE OPCIONES DE CULTIVO A PARTIR DE VARIABLES CLIMATICAS</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>ARIZA RIAÑO MADDYZETH</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Julio Baron Velandia</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Tesis - MODELO DE INFERENCIA ONTOLOGICA PARA CARACTERIZACION DE OPCIONES DE CULTIVO A PARTIR DE VA.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Actualización de grupo</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Se completó GEFEM para un registro previamente no especificado.</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>GIIRA</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Modelo de clasificación de imágenes basado en Multiview Learning</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Kevin Camilo Diaz Monje</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Nancy Yaneth Gelvez Garcia</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Tesis - Modelo de clasificación de imágenes basado en Multiview Learning.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos INVESTIGACION.xlsx</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Diferencia por validar</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Un registro presenta grupos distintos en las fuentes: GITUD y GIIRA.</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>GITUD</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Metodología comparativa para modelos de lenguaje de gran tamaño y algorítmos de aprendizaje automático usando internet de las cosas y computación en la nube con aplicaciones en predicción meteorológica.</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Ivan Dario Bello González</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Elvis Eduardo Gaona García</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Tesis - Metodología comparativa para modelos de lenguaje de gran tamaño y algorítmos de aprendizaj.pdf</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>MCIC - Base de datos Profundizacion.xlsx</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Un trabajo de profundización sustentado en 2026 y tres pasantías con acta de 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Programación sustentaciones.xlsx</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Registros nuevos</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Sustentaciones efectivamente realizadas y registradas en 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Programación sustentaciones.xlsx</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Registros cruzados</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Se completaron fechas, actas, títulos o directores sin duplicar registros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Programación sustentaciones.xlsx</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Casos pendientes</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Casos programados o radicados sin sustentación efectiva: diez registros nuevos y uno reclasificado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Solicitud MCIC - Trabajos de grado grupop LIDER.xlsx</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cruce de 10 casos únicos</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Cinco registros existentes fueron actualizados con el grupo LIDER y cinco casos avalados se incorporaron sin sustentación verificada; dos filas repetían trabajos con otro año de aval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Trabajos de Grado Avalados – Maestría en Ciencias de la Información y las Comunicaciones (2022–2026) (1).xlsx</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Registros cruzados GEFEM</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Los 17 registros ya existían y contaban con enlace RIUD: ocho conservaron GEFEM, ocho se actualizaron desde grupo no especificado y uno presentó diferencia con INTERNET INTELIGENTE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Directorio institucional de grupos — Unidad de Investigaciones</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Cruce nominal de directores</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Cinco asociaciones se verificaron explícitamente en el portal institucional y trece se completaron por coincidencia nominal consistente con registros ya clasificados; siete casos permanecen pendientes de validación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Total de casos</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>148 registros</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Trabajos sustentados</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>133 registros</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Pendientes o sin sustentación verificada</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>15 registros</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Registros adicionales</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Coincidencias integradas sin duplicar</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Grupos identificados</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Soporte de grupo verificado</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>100% de casos con grupo</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Enlaces RIUD disponibles</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>17 registros</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Ventana temporal</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>2022–2026</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Método: se incluyeron todos los casos localizados para la ventana 2022–2026 vinculados con grupos de investigación. Los registros con fecha efectiva de sustentación, año de grado, acta de pasantía o enlace RIUD se clasificaron como sustentados. Los casos únicamente programados, radicados o avalados por un grupo se conservaron como no sustentados o sin sustentación verificada y sí se contabilizan en los gráficos y en la matriz, diferenciados por estado. Los años de la base LIDER corresponden a la emisión del aval y no sustituyen el año efectivo de sustentación. La base GEFEM se cruzó completamente con registros existentes que ya contaban con enlace RIUD. Para los grupos de investigación se contrastaron las cartas de aval, radicaciones y expedientes documentales en Bronze. Las diferencias entre fuentes se conservaron en la columna Observación de cruce.</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Multimedia Interactiva y Animación Digital</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Modelo de sistemas multi-agentes para la consulta basada en niveles de confianza sobre recursos abiertos vinculados mediante Linked Open Data</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Camilo Alejandro Valencia Martinez</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Paulo Alonso Gaona García</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Sustentado</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Tesis - Modelo de sistemas multi-agentes para la consulta basada en niveles de confianza sobre rec.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <autoFilter ref="A4:G12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx
+++ b/Data/Bronze/MCIC.INVESTIGACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 8. APORTES DE LA INVESTIGACIÓN, LA INNOVACIÓN, EL DESARROLLO TECNOLÓGICO Y LA CREACIÓN ASOCIADOS AL PROGRAMA ACADÉMICO/b. Socialización y vinculación de actividades de investigación/F8_Trabajos_de_grado_por_grupo_Investigacion.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Versión por modalidad del «Consolidado de trabajos de grado MCIC 2022-2026» (el libro completo del consolidado es el documento de origen). Se omiten el código estudiantil y la ruta del archivo fuente.</t>
+          <t>Versión por modalidad del «Consolidado de trabajos de grado MCIC 2022-2026» (el libro completo del consolidado es el documento de origen). Se omiten el código estudiantil y la ruta del archivo fuente. El consolidado completo está en la misma carpeta (sin el código estudiantil ni las rutas internas).</t>
         </is>
       </c>
     </row>
@@ -1243,66 +1243,66 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>GITEM</t>
+          <t>GICOGE</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>GICOGE</t>
+          <t>GITEM</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Multimedia Interactiva y Animación Digital</t>
+          <t>GIIRA</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>GRECO</t>
+          <t>Multimedia Interactiva y Animación Digital</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>GIIRA</t>
+          <t>GRECO</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1373,7 +1373,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>IAFT</t>
+          <t>GICOECOL</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
@@ -1399,7 +1399,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>GICOECOL</t>
+          <t>IAFT</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -1412,20 +1412,20 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>GITEM++</t>
+          <t>COMPLEX UD</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Bionanotecnología</t>
+          <t>LAMIC</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -1438,7 +1438,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>COMPLEX UD</t>
+          <t>Bionanotecnología</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -1451,66 +1451,66 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>DIMSI</t>
+          <t>CEPMS</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>XUE</t>
+          <t>PROPROBOS</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>CEPMS</t>
+          <t>DIMSI</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>PROPROBOS</t>
+          <t>XUE</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>LAMIC</t>
+          <t>GITEM++</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
